--- a/My 3-Statement Model Visa (Links Brkn)2.xlsx
+++ b/My 3-Statement Model Visa (Links Brkn)2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ephra\OneDrive\Desktop\3-Statement Model Visa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022721DC-915B-4191-85C7-1874EE362E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA24A0B-1BA4-4B2F-B852-8FF292AF516E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{964B22D8-42B5-47E9-A229-95F7D57B30E0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="163">
   <si>
     <t>Income Statement:</t>
   </si>
@@ -523,6 +523,9 @@
   </si>
   <si>
     <t>Common stock, $0.0001 par value</t>
+  </si>
+  <si>
+    <t>Balance Check</t>
   </si>
 </sst>
 </file>
@@ -1101,14 +1104,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D331CDC-E640-4DD2-B051-E368A3962B8F}">
-  <dimension ref="B1:J172"/>
+  <dimension ref="B1:J174"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
     <col min="2" max="2" width="93.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
@@ -2162,15 +2166,15 @@
         <v>109</v>
       </c>
       <c r="C38" s="34">
-        <f>ABS(C141)/C48</f>
+        <f>ABS(C143)/C48</f>
         <v>3.2431935809879645E-2</v>
       </c>
       <c r="D38" s="34">
-        <f>ABS(D141)/D48</f>
+        <f>ABS(D143)/D48</f>
         <v>3.498858765239659E-2</v>
       </c>
       <c r="E38" s="34">
-        <f>ABS(E141)/E48</f>
+        <f>ABS(E143)/E48</f>
         <v>3.705E-2</v>
       </c>
       <c r="F38" s="34">
@@ -2194,15 +2198,15 @@
         <v>107</v>
       </c>
       <c r="C39" s="34">
-        <f>C124/C48</f>
+        <f>C126/C48</f>
         <v>2.3428168927816739E-2</v>
       </c>
       <c r="D39" s="34">
-        <f>D124/D48</f>
+        <f>D126/D48</f>
         <v>2.3659745031453544E-2</v>
       </c>
       <c r="E39" s="34">
-        <f>E124/E48</f>
+        <f>E126/E48</f>
         <v>2.2425E-2</v>
       </c>
       <c r="F39" s="34">
@@ -2226,15 +2230,15 @@
         <v>111</v>
       </c>
       <c r="C40" s="34">
-        <f>SUM(C131:C138)/C48</f>
+        <f>SUM(C133:C140)/C48</f>
         <v>-0.30692432548311027</v>
       </c>
       <c r="D40" s="34">
-        <f>SUM(D131:D138)/D48</f>
+        <f>SUM(D133:D140)/D48</f>
         <v>-0.42954962979457773</v>
       </c>
       <c r="E40" s="34">
-        <f>SUM(E131:E138)/E48</f>
+        <f>SUM(E133:E140)/E48</f>
         <v>-0.37930000000000003</v>
       </c>
       <c r="F40" s="34">
@@ -2258,15 +2262,15 @@
         <v>108</v>
       </c>
       <c r="C41" s="34">
-        <f>ABS(C152)/C48</f>
+        <f>ABS(C154)/C48</f>
         <v>0.11487459038985698</v>
       </c>
       <c r="D41" s="34">
-        <f>ABS(D152)/D48</f>
+        <f>ABS(D154)/D48</f>
         <v>0.11738017035016422</v>
       </c>
       <c r="E41" s="34">
-        <f>ABS(E152)/E48</f>
+        <f>ABS(E154)/E48</f>
         <v>0.11584999999999999</v>
       </c>
       <c r="F41" s="34">
@@ -2290,15 +2294,15 @@
         <v>135</v>
       </c>
       <c r="C42" s="34">
-        <f>ABS(C133)/C48</f>
+        <f>ABS(C135)/C48</f>
         <v>0.33730438244571709</v>
       </c>
       <c r="D42" s="34">
-        <f>ABS(D133)/D48</f>
+        <f>ABS(D135)/D48</f>
         <v>0.39155486277347884</v>
       </c>
       <c r="E42" s="34">
-        <f>ABS(E133)/E48</f>
+        <f>ABS(E135)/E48</f>
         <v>0.38285000000000002</v>
       </c>
       <c r="F42" s="34">
@@ -2323,15 +2327,15 @@
         <v>112</v>
       </c>
       <c r="C43" s="34">
-        <f>ABS(C150)/C48</f>
+        <f>ABS(C152)/C48</f>
         <v>0.37059381986341222</v>
       </c>
       <c r="D43" s="34">
-        <f>ABS(D150)/D48</f>
+        <f>ABS(D152)/D48</f>
         <v>0.46520625730668597</v>
       </c>
       <c r="E43" s="34">
-        <f>ABS(E150)/E48</f>
+        <f>ABS(E152)/E48</f>
         <v>0.45789999999999997</v>
       </c>
       <c r="F43" s="34">
@@ -2360,15 +2364,15 @@
         <v>137</v>
       </c>
       <c r="C44" s="34">
-        <f>C154/C48</f>
+        <f>C156/C48</f>
         <v>7.9625149297154925E-3</v>
       </c>
       <c r="D44" s="34">
-        <f>D154/D48</f>
+        <f>D156/D48</f>
         <v>9.3247230418081611E-3</v>
       </c>
       <c r="E44" s="34">
-        <f>E154/E48</f>
+        <f>E156/E48</f>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="F44" s="34">
@@ -2392,15 +2396,15 @@
         <v>136</v>
       </c>
       <c r="C45" s="33">
-        <f>ABS(C155)/C48</f>
+        <f>ABS(C157)/C48</f>
         <v>3.9812574648577462E-3</v>
       </c>
       <c r="D45" s="33">
-        <f>ABS(D155)/D48</f>
+        <f>ABS(D157)/D48</f>
         <v>5.7896787841674553E-3</v>
       </c>
       <c r="E45" s="33">
-        <f>ABS(E155)/E48</f>
+        <f>ABS(E157)/E48</f>
         <v>7.025E-3</v>
       </c>
       <c r="F45" s="33">
@@ -3026,11 +3030,26 @@
       <c r="E67" s="45">
         <v>10.199999999999999</v>
       </c>
-      <c r="F67" s="45"/>
-      <c r="G67" s="45"/>
-      <c r="H67" s="45"/>
-      <c r="I67" s="45"/>
-      <c r="J67" s="45"/>
+      <c r="F67" s="45">
+        <f>F65/F72</f>
+        <v>12.225639721417954</v>
+      </c>
+      <c r="G67" s="45">
+        <f t="shared" ref="G67:J67" si="14">G65/G72</f>
+        <v>13.784485689370165</v>
+      </c>
+      <c r="H67" s="45">
+        <f t="shared" si="14"/>
+        <v>15.531743160872498</v>
+      </c>
+      <c r="I67" s="45">
+        <f t="shared" si="14"/>
+        <v>17.616933339773034</v>
+      </c>
+      <c r="J67" s="45">
+        <f t="shared" si="14"/>
+        <v>19.863343360751095</v>
+      </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="5" t="s">
@@ -3045,11 +3064,21 @@
       <c r="E68" s="45">
         <v>15.95</v>
       </c>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="45"/>
-      <c r="I68" s="45"/>
-      <c r="J68" s="45"/>
+      <c r="F68" s="45">
+        <v>0</v>
+      </c>
+      <c r="G68" s="45">
+        <v>0</v>
+      </c>
+      <c r="H68" s="45">
+        <v>0</v>
+      </c>
+      <c r="I68" s="45">
+        <v>0</v>
+      </c>
+      <c r="J68" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="5" t="s">
@@ -3064,11 +3093,21 @@
       <c r="E69" s="45">
         <v>15.7</v>
       </c>
-      <c r="F69" s="45"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="45"/>
-      <c r="I69" s="45"/>
-      <c r="J69" s="45"/>
+      <c r="F69" s="45">
+        <v>0</v>
+      </c>
+      <c r="G69" s="45">
+        <v>0</v>
+      </c>
+      <c r="H69" s="45">
+        <v>0</v>
+      </c>
+      <c r="I69" s="45">
+        <v>0</v>
+      </c>
+      <c r="J69" s="45">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="26" t="s">
@@ -3083,11 +3122,21 @@
       <c r="E70" s="46">
         <v>40.82</v>
       </c>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
+      <c r="F70" s="46">
+        <v>0</v>
+      </c>
+      <c r="G70" s="46">
+        <v>0</v>
+      </c>
+      <c r="H70" s="46">
+        <v>0</v>
+      </c>
+      <c r="I70" s="46">
+        <v>0</v>
+      </c>
+      <c r="J70" s="46">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="4" t="s">
@@ -3115,11 +3164,26 @@
       <c r="E72" s="30">
         <v>1966</v>
       </c>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-      <c r="J72" s="30"/>
+      <c r="F72" s="30">
+        <f>E72*(1-2.5/100)</f>
+        <v>1916.85</v>
+      </c>
+      <c r="G72" s="30">
+        <f t="shared" ref="G72:J72" si="15">F72*(1-2.5/100)</f>
+        <v>1868.9287499999998</v>
+      </c>
+      <c r="H72" s="30">
+        <f t="shared" si="15"/>
+        <v>1822.2055312499997</v>
+      </c>
+      <c r="I72" s="30">
+        <f t="shared" si="15"/>
+        <v>1776.6503929687497</v>
+      </c>
+      <c r="J72" s="30">
+        <f t="shared" si="15"/>
+        <v>1732.2341331445309</v>
+      </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="5" t="s">
@@ -3134,11 +3198,21 @@
       <c r="E73" s="30">
         <v>5</v>
       </c>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="30"/>
-      <c r="J73" s="30"/>
+      <c r="F73" s="30">
+        <v>0</v>
+      </c>
+      <c r="G73" s="30">
+        <v>0</v>
+      </c>
+      <c r="H73" s="30">
+        <v>0</v>
+      </c>
+      <c r="I73" s="30">
+        <v>0</v>
+      </c>
+      <c r="J73" s="30">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="5" t="s">
@@ -3153,11 +3227,21 @@
       <c r="E74" s="30">
         <v>120</v>
       </c>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
-      <c r="J74" s="30"/>
+      <c r="F74" s="30">
+        <v>0</v>
+      </c>
+      <c r="G74" s="30">
+        <v>0</v>
+      </c>
+      <c r="H74" s="30">
+        <v>0</v>
+      </c>
+      <c r="I74" s="30">
+        <v>0</v>
+      </c>
+      <c r="J74" s="30">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="44" t="s">
@@ -3172,11 +3256,21 @@
       <c r="E75" s="47">
         <v>9</v>
       </c>
-      <c r="F75" s="47"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
-      <c r="J75" s="47"/>
+      <c r="F75" s="47">
+        <v>0</v>
+      </c>
+      <c r="G75" s="47">
+        <v>0</v>
+      </c>
+      <c r="H75" s="47">
+        <v>0</v>
+      </c>
+      <c r="I75" s="47">
+        <v>0</v>
+      </c>
+      <c r="J75" s="47">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
@@ -3226,24 +3320,24 @@
         <v>17164</v>
       </c>
       <c r="F79" s="30">
-        <f>F18*F48</f>
-        <v>17280</v>
+        <f>F163-F80</f>
+        <v>38853.128757407001</v>
       </c>
       <c r="G79" s="30">
-        <f>G18*G48</f>
-        <v>18022.773888989501</v>
+        <f t="shared" ref="G79:J79" si="16">G163-G80</f>
+        <v>56771.202068829909</v>
       </c>
       <c r="H79" s="30">
-        <f>H18*H48</f>
-        <v>18747.479112736237</v>
+        <f t="shared" si="16"/>
+        <v>76395.401103516633</v>
       </c>
       <c r="I79" s="30">
-        <f>I18*I48</f>
-        <v>19441.135839907482</v>
+        <f t="shared" si="16"/>
+        <v>98326.927265268168</v>
       </c>
       <c r="J79" s="30">
-        <f>J18*J48</f>
-        <v>20089.957606723568</v>
+        <f t="shared" si="16"/>
+        <v>121870.10762786066</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.25">
@@ -3430,24 +3524,24 @@
         <v>2158</v>
       </c>
       <c r="F85" s="30">
-        <f>F32*F48</f>
-        <v>11232</v>
+        <f>F25*F48</f>
+        <v>5400</v>
       </c>
       <c r="G85" s="30">
-        <f>G32*G48</f>
-        <v>12331.371608255975</v>
+        <f t="shared" ref="G85:J85" si="17">G25*G48</f>
+        <v>5928.5440424307571</v>
       </c>
       <c r="H85" s="30">
-        <f>H32*H48</f>
-        <v>13539.846025865061</v>
+        <f t="shared" si="17"/>
+        <v>6717.8466820638196</v>
       </c>
       <c r="I85" s="30">
-        <f>I32*I48</f>
-        <v>14866.750936399838</v>
+        <f t="shared" si="17"/>
+        <v>7376.195656906074</v>
       </c>
       <c r="J85" s="30">
-        <f>J32*J48</f>
-        <v>16323.090555462899</v>
+        <f t="shared" si="17"/>
+        <v>8098.7641602104386</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.25">
@@ -3499,23 +3593,23 @@
       </c>
       <c r="F87" s="30">
         <f>SUM(F79:F86)</f>
-        <v>49732.4</v>
+        <v>65473.528757407003</v>
       </c>
       <c r="G87" s="30">
-        <f t="shared" ref="G87:J87" si="14">SUM(G79:G86)</f>
-        <v>53358.910184491717</v>
+        <f t="shared" ref="G87:J87" si="18">SUM(G79:G86)</f>
+        <v>85704.51079850689</v>
       </c>
       <c r="H87" s="30">
-        <f t="shared" si="14"/>
-        <v>56732.773456510549</v>
+        <f t="shared" si="18"/>
+        <v>107558.6961034897</v>
       </c>
       <c r="I87" s="30">
-        <f t="shared" si="14"/>
-        <v>60855.969029371678</v>
+        <f t="shared" si="18"/>
+        <v>132251.2051752386</v>
       </c>
       <c r="J87" s="30">
-        <f t="shared" si="14"/>
-        <v>65268.86858084306</v>
+        <f t="shared" si="18"/>
+        <v>158824.69220672769</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.25">
@@ -3600,23 +3694,23 @@
         <v>4236</v>
       </c>
       <c r="F90" s="30">
-        <f>E90+ABS(F141)-F125</f>
+        <f>E90+ABS(F143)-F127</f>
         <v>3807.0845475000006</v>
       </c>
       <c r="G90" s="30">
-        <f>F90+ABS(G141)-G125</f>
+        <f>F90+ABS(G143)-G127</f>
         <v>3337.4361768432345</v>
       </c>
       <c r="H90" s="30">
-        <f>G90+ABS(H141)-H125</f>
+        <f>G90+ABS(H143)-H127</f>
         <v>2822.3212977966414</v>
       </c>
       <c r="I90" s="30">
-        <f>H90+ABS(I141)-I125</f>
+        <f>H90+ABS(I143)-I127</f>
         <v>2353.4737688335781</v>
       </c>
       <c r="J90" s="30">
-        <f>I90+ABS(J141)-J125</f>
+        <f>I90+ABS(J143)-J127</f>
         <v>1840.3238927030429</v>
       </c>
     </row>
@@ -3732,23 +3826,23 @@
       </c>
       <c r="F94" s="38">
         <f>SUM(F87:F93)</f>
-        <v>113011.38400170952</v>
+        <v>128752.51275911651</v>
       </c>
       <c r="G94" s="38">
-        <f t="shared" ref="G94:J94" si="15">SUM(G87:G93)</f>
-        <v>117453.8566640404</v>
+        <f t="shared" ref="G94:J94" si="19">SUM(G87:G93)</f>
+        <v>149799.45727805558</v>
       </c>
       <c r="H94" s="38">
-        <f t="shared" si="15"/>
-        <v>121609.39106667778</v>
+        <f t="shared" si="19"/>
+        <v>172435.31371365691</v>
       </c>
       <c r="I94" s="38">
-        <f t="shared" si="15"/>
-        <v>126687.61014918816</v>
+        <f t="shared" si="19"/>
+        <v>198082.84629505509</v>
       </c>
       <c r="J94" s="38">
-        <f t="shared" si="15"/>
-        <v>132150.1242619082</v>
+        <f t="shared" si="19"/>
+        <v>225705.94788779283</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.25">
@@ -4041,19 +4135,19 @@
         <v>28944</v>
       </c>
       <c r="G104" s="30">
-        <f t="shared" ref="G104:J104" si="16">SUM(G96:G103)</f>
+        <f t="shared" ref="G104:J104" si="20">SUM(G96:G103)</f>
         <v>31302.712544034399</v>
       </c>
       <c r="H104" s="30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>33797.538733793946</v>
       </c>
       <c r="I104" s="30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>36537.899416767301</v>
       </c>
       <c r="J104" s="30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>39489.322920716011</v>
       </c>
     </row>
@@ -4318,23 +4412,23 @@
         <v>15106</v>
       </c>
       <c r="F114" s="30">
-        <f>E114+F65+F152+F150</f>
+        <f>E114+F65+F154+F152</f>
         <v>14727.436388750586</v>
       </c>
       <c r="G114" s="30">
-        <f t="shared" ref="G114:J114" si="17">F114+G65+G152+G150</f>
+        <f>F114+G65+G154+G152</f>
         <v>13386.89021279358</v>
       </c>
       <c r="H114" s="30">
-        <f t="shared" si="17"/>
+        <f>G114+H65+H154+H152</f>
         <v>11908.54971320292</v>
       </c>
       <c r="I114" s="30">
-        <f t="shared" si="17"/>
+        <f>H114+I65+I154+I152</f>
         <v>10719.258669381139</v>
       </c>
       <c r="J114" s="30">
-        <f t="shared" si="17"/>
+        <f>I114+J65+J154+J152</f>
         <v>8892.3350740917231</v>
       </c>
     </row>
@@ -4385,372 +4479,378 @@
         <v>37530.43638875059</v>
       </c>
       <c r="G116" s="30">
-        <f t="shared" ref="G116:J116" si="18">SUM(G110:G115)</f>
+        <f t="shared" ref="G116:J116" si="21">SUM(G110:G115)</f>
         <v>36189.89021279358</v>
       </c>
       <c r="H116" s="30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>34711.54971320292</v>
       </c>
       <c r="I116" s="30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>33522.258669381139</v>
       </c>
       <c r="J116" s="30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>31695.335074091723</v>
       </c>
     </row>
-    <row r="117" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="48" t="s">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B117" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C117" s="36">
+      <c r="C117" s="37">
         <v>90499</v>
       </c>
-      <c r="D117" s="36">
+      <c r="D117" s="37">
         <v>94511</v>
       </c>
-      <c r="E117" s="36">
+      <c r="E117" s="37">
         <v>99627</v>
       </c>
-      <c r="F117" s="36">
+      <c r="F117" s="37">
         <f>F108+F116</f>
         <v>93785.43638875059</v>
       </c>
-      <c r="G117" s="36">
-        <f t="shared" ref="G117:J117" si="19">G108+G116</f>
+      <c r="G117" s="37">
+        <f t="shared" ref="G117:J117" si="22">G108+G116</f>
         <v>94540.73685040581</v>
       </c>
-      <c r="H117" s="36">
-        <f t="shared" si="19"/>
+      <c r="H117" s="37">
+        <f t="shared" si="22"/>
         <v>95222.378373058222</v>
       </c>
-      <c r="I117" s="36">
-        <f t="shared" si="19"/>
+      <c r="I117" s="37">
+        <f t="shared" si="22"/>
         <v>96354.754312025354</v>
       </c>
-      <c r="J117" s="36">
-        <f t="shared" si="19"/>
+      <c r="J117" s="37">
+        <f t="shared" si="22"/>
         <v>96963.469170017837</v>
       </c>
     </row>
+    <row r="118" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B118" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="C118" s="36">
+        <f>C117-C94</f>
+        <v>0</v>
+      </c>
+      <c r="D118" s="36">
+        <f t="shared" ref="D118:J118" si="23">D117-D94</f>
+        <v>0</v>
+      </c>
+      <c r="E118" s="36">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F118" s="36">
+        <f t="shared" si="23"/>
+        <v>-34967.076370365918</v>
+      </c>
+      <c r="G118" s="36">
+        <f t="shared" si="23"/>
+        <v>-55258.720427649765</v>
+      </c>
+      <c r="H118" s="36">
+        <f t="shared" si="23"/>
+        <v>-77212.935340598691</v>
+      </c>
+      <c r="I118" s="36">
+        <f t="shared" si="23"/>
+        <v>-101728.09198302974</v>
+      </c>
+      <c r="J118" s="36">
+        <f t="shared" si="23"/>
+        <v>-128742.478717775</v>
+      </c>
+    </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="4"/>
+      <c r="C119" s="37"/>
+      <c r="D119" s="37"/>
+      <c r="E119" s="37"/>
+      <c r="F119" s="37"/>
+      <c r="G119" s="37"/>
+      <c r="H119" s="37"/>
+      <c r="I119" s="37"/>
+      <c r="J119" s="37"/>
+    </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C121" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D121" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="E121" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F119" s="2" t="s">
+      <c r="F121" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="G121" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="H121" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I119" s="2" t="s">
+      <c r="I121" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J119" s="2" t="s">
+      <c r="J121" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B120" s="10" t="s">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B122" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B121" s="8" t="s">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B123" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C121" s="37">
+      <c r="C123" s="37">
         <v>17273</v>
       </c>
-      <c r="D121" s="37">
+      <c r="D123" s="37">
         <v>19743</v>
       </c>
-      <c r="E121" s="37">
+      <c r="E123" s="37">
         <v>20058</v>
       </c>
-      <c r="F121" s="37">
+      <c r="F123" s="37">
         <f>F65</f>
         <v>23434.717500000002</v>
       </c>
-      <c r="G121" s="37">
+      <c r="G123" s="37">
         <f>G65</f>
         <v>25762.221608827469</v>
       </c>
-      <c r="H121" s="37">
+      <c r="H123" s="37">
         <f>H65</f>
         <v>28302.028297696219</v>
       </c>
-      <c r="I121" s="37">
+      <c r="I123" s="37">
         <f>I65</f>
         <v>31299.13154101203</v>
       </c>
-      <c r="J121" s="37">
+      <c r="J123" s="37">
         <f>J65</f>
         <v>34407.961367862845</v>
       </c>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B122" s="10" t="s">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B124" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B123" s="9" t="s">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B125" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C123" s="30">
+      <c r="C125" s="30">
         <v>12297</v>
       </c>
-      <c r="D123" s="30">
+      <c r="D125" s="30">
         <v>13764</v>
       </c>
-      <c r="E123" s="30">
+      <c r="E125" s="30">
         <v>15751</v>
       </c>
-      <c r="F123" s="30">
+      <c r="F125" s="30">
         <f>F42*F48</f>
         <v>16008.61313115642</v>
       </c>
-      <c r="G123" s="30">
+      <c r="G125" s="30">
         <f>G42*G48</f>
         <v>17927.917184310609</v>
       </c>
-      <c r="H123" s="30">
+      <c r="H125" s="30">
         <f>H42*H48</f>
         <v>19736.929399241762</v>
       </c>
-      <c r="I123" s="30">
+      <c r="I125" s="30">
         <f>I42*I48</f>
         <v>21728.328291661303</v>
       </c>
-      <c r="J123" s="30">
+      <c r="J125" s="30">
         <f>J42*J48</f>
         <v>23856.824657984234</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B124" s="9" t="s">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B126" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C124" s="30">
+      <c r="C126" s="30">
         <v>765</v>
       </c>
-      <c r="D124" s="30">
+      <c r="D126" s="30">
         <v>850</v>
       </c>
-      <c r="E124" s="30">
+      <c r="E126" s="30">
         <v>897</v>
       </c>
-      <c r="F124" s="30">
-        <f>F121*F39</f>
+      <c r="F126" s="30">
+        <f>F123*F39</f>
         <v>515.56378500000005</v>
       </c>
-      <c r="G124" s="30">
-        <f>G121*G39</f>
+      <c r="G126" s="30">
+        <f>G123*G39</f>
         <v>566.76887539420431</v>
       </c>
-      <c r="H124" s="30">
-        <f>H121*H39</f>
+      <c r="H126" s="30">
+        <f>H123*H39</f>
         <v>594.34259425162065</v>
       </c>
-      <c r="I124" s="30">
-        <f>I121*I39</f>
+      <c r="I126" s="30">
+        <f>I123*I39</f>
         <v>657.28176236125262</v>
       </c>
-      <c r="J124" s="30">
-        <f>J121*J39</f>
+      <c r="J126" s="30">
+        <f>J123*J39</f>
         <v>722.56718872511976</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B125" s="9" t="s">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B127" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C125" s="30">
+      <c r="C127" s="30">
         <v>943</v>
       </c>
-      <c r="D125" s="30">
+      <c r="D127" s="30">
         <v>1034</v>
       </c>
-      <c r="E125" s="30">
+      <c r="E127" s="30">
         <v>1220</v>
       </c>
-      <c r="F125" s="30">
+      <c r="F127" s="30">
         <f>F54</f>
         <v>1296</v>
       </c>
-      <c r="G125" s="30">
+      <c r="G127" s="30">
         <f>G54</f>
         <v>1422.8505701833817</v>
       </c>
-      <c r="H125" s="30">
+      <c r="H127" s="30">
         <f>H54</f>
         <v>1562.2899260613533</v>
       </c>
-      <c r="I125" s="30">
+      <c r="I127" s="30">
         <f>I54</f>
         <v>1658.2145275215205</v>
       </c>
-      <c r="J125" s="30">
+      <c r="J127" s="30">
         <f>J54</f>
         <v>1820.6524081093235</v>
       </c>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B126" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C126" s="30">
-        <v>-483</v>
-      </c>
-      <c r="D126" s="30">
-        <v>-100</v>
-      </c>
-      <c r="E126" s="30">
-        <v>152</v>
-      </c>
-      <c r="F126" s="30">
-        <v>152</v>
-      </c>
-      <c r="G126" s="30">
-        <v>152</v>
-      </c>
-      <c r="H126" s="30">
-        <v>152</v>
-      </c>
-      <c r="I126" s="30">
-        <v>152</v>
-      </c>
-      <c r="J126" s="30">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B127" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C127" s="30">
-        <v>-136</v>
-      </c>
-      <c r="D127" s="30">
-        <v>-139</v>
-      </c>
-      <c r="E127" s="30">
-        <v>-28</v>
-      </c>
-      <c r="F127" s="30">
-        <v>0</v>
-      </c>
-      <c r="G127" s="30">
-        <v>0</v>
-      </c>
-      <c r="H127" s="30">
-        <v>0</v>
-      </c>
-      <c r="I127" s="30">
-        <v>0</v>
-      </c>
-      <c r="J127" s="30">
-        <v>0</v>
-      </c>
-    </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C128" s="30">
-        <v>104</v>
+        <v>-483</v>
       </c>
       <c r="D128" s="30">
-        <v>94</v>
+        <v>-100</v>
       </c>
       <c r="E128" s="30">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="F128" s="30">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="G128" s="30">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H128" s="30">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="I128" s="30">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="J128" s="30">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C129" s="30">
-        <v>14</v>
+        <v>-136</v>
       </c>
       <c r="D129" s="30">
-        <v>136</v>
+        <v>-139</v>
       </c>
       <c r="E129" s="30">
+        <v>-28</v>
+      </c>
+      <c r="F129" s="30">
+        <v>0</v>
+      </c>
+      <c r="G129" s="30">
+        <v>0</v>
+      </c>
+      <c r="H129" s="30">
+        <v>0</v>
+      </c>
+      <c r="I129" s="30">
+        <v>0</v>
+      </c>
+      <c r="J129" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B130" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C130" s="30">
+        <v>104</v>
+      </c>
+      <c r="D130" s="30">
         <v>94</v>
       </c>
-      <c r="F129" s="30">
-        <v>0</v>
-      </c>
-      <c r="G129" s="30">
-        <v>0</v>
-      </c>
-      <c r="H129" s="30">
-        <v>0</v>
-      </c>
-      <c r="I129" s="30">
-        <v>0</v>
-      </c>
-      <c r="J129" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B130" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C130" s="30"/>
-      <c r="D130" s="30"/>
-      <c r="E130" s="30"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="30"/>
-      <c r="H130" s="30"/>
-      <c r="I130" s="30"/>
-      <c r="J130" s="30"/>
+      <c r="E130" s="30">
+        <v>87</v>
+      </c>
+      <c r="F130" s="30">
+        <v>0</v>
+      </c>
+      <c r="G130" s="30">
+        <v>0</v>
+      </c>
+      <c r="H130" s="30">
+        <v>0</v>
+      </c>
+      <c r="I130" s="30">
+        <v>0</v>
+      </c>
+      <c r="J130" s="30">
+        <v>0</v>
+      </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="9" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C131" s="30">
-        <v>-160</v>
+        <v>14</v>
       </c>
       <c r="D131" s="30">
-        <v>-2175</v>
+        <v>136</v>
       </c>
       <c r="E131" s="30">
-        <v>374</v>
+        <v>94</v>
       </c>
       <c r="F131" s="30">
         <v>0</v>
@@ -4769,46 +4869,30 @@
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B132" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C132" s="30">
-        <v>-250</v>
-      </c>
-      <c r="D132" s="30">
-        <v>-237</v>
-      </c>
-      <c r="E132" s="30">
-        <v>-542</v>
-      </c>
-      <c r="F132" s="30">
-        <v>0</v>
-      </c>
-      <c r="G132" s="30">
-        <v>0</v>
-      </c>
-      <c r="H132" s="30">
-        <v>0</v>
-      </c>
-      <c r="I132" s="30">
-        <v>0</v>
-      </c>
-      <c r="J132" s="30">
-        <v>0</v>
-      </c>
+      <c r="B132" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C132" s="30"/>
+      <c r="D132" s="30"/>
+      <c r="E132" s="30"/>
+      <c r="F132" s="30"/>
+      <c r="G132" s="30"/>
+      <c r="H132" s="30"/>
+      <c r="I132" s="30"/>
+      <c r="J132" s="30"/>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C133" s="30">
-        <v>-11014</v>
+        <v>-160</v>
       </c>
       <c r="D133" s="30">
-        <v>-14067</v>
+        <v>-2175</v>
       </c>
       <c r="E133" s="30">
-        <v>-15314</v>
+        <v>374</v>
       </c>
       <c r="F133" s="30">
         <v>0</v>
@@ -4828,16 +4912,16 @@
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C134" s="30">
-        <v>-24</v>
+        <v>-250</v>
       </c>
       <c r="D134" s="30">
-        <v>-199</v>
+        <v>-237</v>
       </c>
       <c r="E134" s="30">
-        <v>160</v>
+        <v>-542</v>
       </c>
       <c r="F134" s="30">
         <v>0</v>
@@ -4857,16 +4941,16 @@
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C135" s="30">
-        <v>34</v>
+        <v>-11014</v>
       </c>
       <c r="D135" s="30">
-        <v>109</v>
+        <v>-14067</v>
       </c>
       <c r="E135" s="30">
-        <v>67</v>
+        <v>-15314</v>
       </c>
       <c r="F135" s="30">
         <v>0</v>
@@ -4886,16 +4970,16 @@
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C136" s="30">
-        <v>-194</v>
+        <v>-24</v>
       </c>
       <c r="D136" s="30">
-        <v>1841</v>
+        <v>-199</v>
       </c>
       <c r="E136" s="30">
-        <v>-847</v>
+        <v>160</v>
       </c>
       <c r="F136" s="30">
         <v>0</v>
@@ -4915,16 +4999,16 @@
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C137" s="30">
-        <v>1291</v>
+        <v>34</v>
       </c>
       <c r="D137" s="30">
-        <v>-676</v>
+        <v>109</v>
       </c>
       <c r="E137" s="30">
-        <v>-373</v>
+        <v>67</v>
       </c>
       <c r="F137" s="30">
         <v>0</v>
@@ -4944,176 +5028,176 @@
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C138" s="30">
+        <v>-194</v>
+      </c>
+      <c r="D138" s="30">
+        <v>1841</v>
+      </c>
+      <c r="E138" s="30">
+        <v>-847</v>
+      </c>
+      <c r="F138" s="30">
+        <v>0</v>
+      </c>
+      <c r="G138" s="30">
+        <v>0</v>
+      </c>
+      <c r="H138" s="30">
+        <v>0</v>
+      </c>
+      <c r="I138" s="30">
+        <v>0</v>
+      </c>
+      <c r="J138" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B139" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C139" s="30">
+        <v>1291</v>
+      </c>
+      <c r="D139" s="30">
+        <v>-676</v>
+      </c>
+      <c r="E139" s="30">
+        <v>-373</v>
+      </c>
+      <c r="F139" s="30">
+        <v>0</v>
+      </c>
+      <c r="G139" s="30">
+        <v>0</v>
+      </c>
+      <c r="H139" s="30">
+        <v>0</v>
+      </c>
+      <c r="I139" s="30">
+        <v>0</v>
+      </c>
+      <c r="J139" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B140" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C138" s="30">
+      <c r="C140" s="30">
         <v>295</v>
       </c>
-      <c r="D138" s="30">
+      <c r="D140" s="30">
         <v>-28</v>
       </c>
-      <c r="E138" s="30">
+      <c r="E140" s="30">
         <v>1303</v>
       </c>
-      <c r="F138" s="30">
-        <v>0</v>
-      </c>
-      <c r="G138" s="30">
-        <v>0</v>
-      </c>
-      <c r="H138" s="30">
-        <v>0</v>
-      </c>
-      <c r="I138" s="30">
-        <v>0</v>
-      </c>
-      <c r="J138" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B139" s="11" t="s">
+      <c r="F140" s="30">
+        <v>0</v>
+      </c>
+      <c r="G140" s="30">
+        <v>0</v>
+      </c>
+      <c r="H140" s="30">
+        <v>0</v>
+      </c>
+      <c r="I140" s="30">
+        <v>0</v>
+      </c>
+      <c r="J140" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B141" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C139" s="31">
+      <c r="C141" s="31">
         <v>20755</v>
       </c>
-      <c r="D139" s="31">
+      <c r="D141" s="31">
         <v>19950</v>
       </c>
-      <c r="E139" s="31">
+      <c r="E141" s="31">
         <v>23059</v>
       </c>
-      <c r="F139" s="31">
-        <f>F121+SUM(F123:F129)+F48*F40</f>
+      <c r="F141" s="31">
+        <f>F123+SUM(F125:F131)+F48*F40</f>
         <v>41406.894416156421</v>
       </c>
-      <c r="G139" s="31">
-        <f>G121+SUM(G123:G129)+G48*G40</f>
+      <c r="G141" s="31">
+        <f>G123+SUM(G125:G131)+G48*G40</f>
         <v>45831.758238715665</v>
       </c>
-      <c r="H139" s="31">
-        <f>H121+SUM(H123:H129)+H48*H40</f>
+      <c r="H141" s="31">
+        <f>H123+SUM(H125:H131)+H48*H40</f>
         <v>50347.590217250952</v>
       </c>
-      <c r="I139" s="31">
-        <f>I121+SUM(I123:I129)+I48*I40</f>
+      <c r="I141" s="31">
+        <f>I123+SUM(I125:I131)+I48*I40</f>
         <v>55494.956122556105</v>
       </c>
-      <c r="J139" s="31">
-        <f>J121+SUM(J123:J129)+J48*J40</f>
+      <c r="J141" s="31">
+        <f>J123+SUM(J125:J131)+J48*J40</f>
         <v>60960.005622681521</v>
       </c>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B140" s="10" t="s">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B142" s="10" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B141" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C141" s="30">
-        <v>-1059</v>
-      </c>
-      <c r="D141" s="30">
-        <v>-1257</v>
-      </c>
-      <c r="E141" s="30">
-        <v>-1482</v>
-      </c>
-      <c r="F141" s="30">
-        <f>-F121*F38</f>
-        <v>-867.0845475000001</v>
-      </c>
-      <c r="G141" s="30">
-        <f>-G121*G38</f>
-        <v>-953.20219952661625</v>
-      </c>
-      <c r="H141" s="30">
-        <f>-H121*H38</f>
-        <v>-1047.1750470147601</v>
-      </c>
-      <c r="I141" s="30">
-        <f>-I121*I38</f>
-        <v>-1189.366998558457</v>
-      </c>
-      <c r="J141" s="30">
-        <f>-J121*J38</f>
-        <v>-1307.5025319787881</v>
-      </c>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B142" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C142" s="30">
-        <v>-4363</v>
-      </c>
-      <c r="D142" s="30">
-        <v>-4443</v>
-      </c>
-      <c r="E142" s="30">
-        <v>0</v>
-      </c>
-      <c r="F142" s="30">
-        <v>0</v>
-      </c>
-      <c r="G142" s="30">
-        <v>0</v>
-      </c>
-      <c r="H142" s="30">
-        <v>0</v>
-      </c>
-      <c r="I142" s="30">
-        <v>0</v>
-      </c>
-      <c r="J142" s="30">
-        <v>0</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C143" s="30">
-        <v>3160</v>
+        <v>-1059</v>
       </c>
       <c r="D143" s="30">
-        <v>5013</v>
+        <v>-1257</v>
       </c>
       <c r="E143" s="30">
-        <v>3024</v>
+        <v>-1482</v>
       </c>
       <c r="F143" s="30">
-        <v>0</v>
+        <f>-F123*F38</f>
+        <v>-867.0845475000001</v>
       </c>
       <c r="G143" s="30">
-        <v>0</v>
+        <f>-G123*G38</f>
+        <v>-953.20219952661625</v>
       </c>
       <c r="H143" s="30">
-        <v>0</v>
+        <f>-H123*H38</f>
+        <v>-1047.1750470147601</v>
       </c>
       <c r="I143" s="30">
-        <v>0</v>
+        <f>-I123*I38</f>
+        <v>-1189.366998558457</v>
       </c>
       <c r="J143" s="30">
-        <v>0</v>
+        <f>-J123*J38</f>
+        <v>-1307.5025319787881</v>
       </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C144" s="30">
-        <v>0</v>
+        <v>-4363</v>
       </c>
       <c r="D144" s="30">
-        <v>-915</v>
+        <v>-4443</v>
       </c>
       <c r="E144" s="30">
-        <v>-887</v>
+        <v>0</v>
       </c>
       <c r="F144" s="30">
         <v>0</v>
@@ -5133,16 +5217,16 @@
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C145" s="30">
-        <v>-121</v>
+        <v>3160</v>
       </c>
       <c r="D145" s="30">
-        <v>-231</v>
+        <v>5013</v>
       </c>
       <c r="E145" s="30">
-        <v>-68</v>
+        <v>3024</v>
       </c>
       <c r="F145" s="30">
         <v>0</v>
@@ -5162,16 +5246,16 @@
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C146" s="30">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D146" s="30">
-        <v>0</v>
+        <v>-915</v>
       </c>
       <c r="E146" s="30">
-        <v>0</v>
+        <v>-887</v>
       </c>
       <c r="F146" s="30">
         <v>0</v>
@@ -5191,341 +5275,336 @@
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C147" s="30">
+        <v>-121</v>
+      </c>
+      <c r="D147" s="30">
+        <v>-231</v>
+      </c>
+      <c r="E147" s="30">
+        <v>-68</v>
+      </c>
+      <c r="F147" s="30">
+        <v>0</v>
+      </c>
+      <c r="G147" s="30">
+        <v>0</v>
+      </c>
+      <c r="H147" s="30">
+        <v>0</v>
+      </c>
+      <c r="I147" s="30">
+        <v>0</v>
+      </c>
+      <c r="J147" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B148" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C148" s="30">
+        <v>402</v>
+      </c>
+      <c r="D148" s="30">
+        <v>0</v>
+      </c>
+      <c r="E148" s="30">
+        <v>0</v>
+      </c>
+      <c r="F148" s="30">
+        <v>0</v>
+      </c>
+      <c r="G148" s="30">
+        <v>0</v>
+      </c>
+      <c r="H148" s="30">
+        <v>0</v>
+      </c>
+      <c r="I148" s="30">
+        <v>0</v>
+      </c>
+      <c r="J148" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B149" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C147" s="30">
+      <c r="C149" s="30">
         <v>-25</v>
       </c>
-      <c r="D147" s="30">
+      <c r="D149" s="30">
         <v>-93</v>
       </c>
-      <c r="E147" s="30">
+      <c r="E149" s="30">
         <v>121</v>
       </c>
-      <c r="F147" s="30">
-        <v>0</v>
-      </c>
-      <c r="G147" s="30">
-        <v>0</v>
-      </c>
-      <c r="H147" s="30">
-        <v>0</v>
-      </c>
-      <c r="I147" s="30">
-        <v>0</v>
-      </c>
-      <c r="J147" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B148" s="11" t="s">
+      <c r="F149" s="30">
+        <v>0</v>
+      </c>
+      <c r="G149" s="30">
+        <v>0</v>
+      </c>
+      <c r="H149" s="30">
+        <v>0</v>
+      </c>
+      <c r="I149" s="30">
+        <v>0</v>
+      </c>
+      <c r="J149" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B150" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C148" s="32">
+      <c r="C150" s="32">
         <v>-2006</v>
       </c>
-      <c r="D148" s="32">
+      <c r="D150" s="32">
         <v>-1926</v>
       </c>
-      <c r="E148" s="32">
+      <c r="E150" s="32">
         <v>708</v>
       </c>
-      <c r="F148" s="32">
-        <f>SUM(F141:F147)</f>
+      <c r="F150" s="32">
+        <f>SUM(F143:F149)</f>
         <v>-867.0845475000001</v>
       </c>
-      <c r="G148" s="32">
-        <f t="shared" ref="G148:J148" si="20">SUM(G141:G147)</f>
+      <c r="G150" s="32">
+        <f t="shared" ref="G150:J150" si="24">SUM(G143:G149)</f>
         <v>-953.20219952661625</v>
       </c>
-      <c r="H148" s="32">
-        <f t="shared" si="20"/>
+      <c r="H150" s="32">
+        <f t="shared" si="24"/>
         <v>-1047.1750470147601</v>
       </c>
-      <c r="I148" s="32">
-        <f t="shared" si="20"/>
+      <c r="I150" s="32">
+        <f t="shared" si="24"/>
         <v>-1189.366998558457</v>
       </c>
-      <c r="J148" s="32">
-        <f t="shared" si="20"/>
+      <c r="J150" s="32">
+        <f t="shared" si="24"/>
         <v>-1307.5025319787881</v>
       </c>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B149" s="10" t="s">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B151" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B150" s="9" t="s">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B152" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C150" s="30">
+      <c r="C152" s="30">
         <v>-12101</v>
       </c>
-      <c r="D150" s="30">
+      <c r="D152" s="30">
         <v>-16713</v>
       </c>
-      <c r="E150" s="30">
+      <c r="E152" s="30">
         <v>-18316</v>
       </c>
-      <c r="F150" s="30">
+      <c r="F152" s="30">
         <f>-F43*F48</f>
         <v>-18629.281111249413</v>
       </c>
-      <c r="G150" s="30">
+      <c r="G152" s="30">
         <f>-G43*G48</f>
         <v>-21411.365504050947</v>
       </c>
-      <c r="H150" s="30">
+      <c r="H152" s="30">
         <f>-H43*H48</f>
         <v>-23270.82743869791</v>
       </c>
-      <c r="I150" s="30">
+      <c r="I152" s="30">
         <f>-I43*I48</f>
         <v>-25340.946173103119</v>
       </c>
-      <c r="J150" s="30">
+      <c r="J152" s="30">
         <f>-J43*J48</f>
         <v>-28073.339685420811</v>
       </c>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B151" s="9" t="s">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B153" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C151" s="30">
+      <c r="C153" s="30">
         <v>-2250</v>
       </c>
-      <c r="D151" s="30">
-        <v>0</v>
-      </c>
-      <c r="E151" s="30">
-        <v>0</v>
-      </c>
-      <c r="F151" s="30">
-        <v>0</v>
-      </c>
-      <c r="G151" s="30">
-        <v>0</v>
-      </c>
-      <c r="H151" s="30">
-        <v>0</v>
-      </c>
-      <c r="I151" s="30">
-        <v>0</v>
-      </c>
-      <c r="J151" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B152" s="9" t="s">
+      <c r="D153" s="30">
+        <v>0</v>
+      </c>
+      <c r="E153" s="30">
+        <v>0</v>
+      </c>
+      <c r="F153" s="30">
+        <v>0</v>
+      </c>
+      <c r="G153" s="30">
+        <v>0</v>
+      </c>
+      <c r="H153" s="30">
+        <v>0</v>
+      </c>
+      <c r="I153" s="30">
+        <v>0</v>
+      </c>
+      <c r="J153" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B154" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C152" s="30">
+      <c r="C154" s="30">
         <v>-3751</v>
       </c>
-      <c r="D152" s="30">
+      <c r="D154" s="30">
         <v>-4217</v>
       </c>
-      <c r="E152" s="30">
+      <c r="E154" s="30">
         <v>-4634</v>
       </c>
-      <c r="F152" s="30">
+      <c r="F154" s="30">
         <f>-F41*F48</f>
         <v>-5184</v>
       </c>
-      <c r="G152" s="30">
+      <c r="G154" s="30">
         <f>-G41*G48</f>
         <v>-5691.4022807335268</v>
       </c>
-      <c r="H152" s="30">
+      <c r="H154" s="30">
         <f>-H41*H48</f>
         <v>-6509.5413585889719</v>
       </c>
-      <c r="I152" s="30">
+      <c r="I154" s="30">
         <f>-I41*I48</f>
         <v>-7147.4764117306913</v>
       </c>
-      <c r="J152" s="30">
+      <c r="J154" s="30">
         <f>-J41*J48</f>
         <v>-8161.5452777314495</v>
       </c>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B153" s="9" t="s">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B155" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C153" s="30">
-        <v>0</v>
-      </c>
-      <c r="D153" s="30">
-        <v>0</v>
-      </c>
-      <c r="E153" s="30">
+      <c r="C155" s="30">
+        <v>0</v>
+      </c>
+      <c r="D155" s="30">
+        <v>0</v>
+      </c>
+      <c r="E155" s="30">
         <v>3924</v>
       </c>
-      <c r="F153" s="30">
-        <v>0</v>
-      </c>
-      <c r="G153" s="30">
-        <v>0</v>
-      </c>
-      <c r="H153" s="30">
-        <v>0</v>
-      </c>
-      <c r="I153" s="30">
-        <v>0</v>
-      </c>
-      <c r="J153" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B154" s="9" t="s">
+      <c r="F155" s="30">
+        <v>0</v>
+      </c>
+      <c r="G155" s="30">
+        <v>0</v>
+      </c>
+      <c r="H155" s="30">
+        <v>0</v>
+      </c>
+      <c r="I155" s="30">
+        <v>0</v>
+      </c>
+      <c r="J155" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B156" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C154" s="30">
+      <c r="C156" s="30">
         <v>260</v>
       </c>
-      <c r="D154" s="30">
+      <c r="D156" s="30">
         <v>335</v>
       </c>
-      <c r="E154" s="30">
+      <c r="E156" s="30">
         <v>396</v>
       </c>
-      <c r="F154" s="30">
+      <c r="F156" s="30">
         <f>F48*F44</f>
         <v>432</v>
       </c>
-      <c r="G154" s="30">
+      <c r="G156" s="30">
         <f>G48*G44</f>
         <v>474.28352339446059</v>
       </c>
-      <c r="H154" s="30">
+      <c r="H156" s="30">
         <f>H48*H44</f>
         <v>520.76330868711773</v>
       </c>
-      <c r="I154" s="30">
+      <c r="I156" s="30">
         <f>I48*I44</f>
         <v>571.79811293845535</v>
       </c>
-      <c r="J154" s="30">
+      <c r="J156" s="30">
         <f>J48*J44</f>
         <v>627.81117521011151</v>
       </c>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B155" s="9" t="s">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B157" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C155" s="30">
+      <c r="C157" s="30">
         <v>-130</v>
       </c>
-      <c r="D155" s="30">
+      <c r="D157" s="30">
         <v>-208</v>
       </c>
-      <c r="E155" s="30">
+      <c r="E157" s="30">
         <v>-281</v>
       </c>
-      <c r="F155" s="30">
+      <c r="F157" s="30">
         <f>-F45*F48</f>
         <v>-302.40000000000003</v>
       </c>
-      <c r="G155" s="30">
+      <c r="G157" s="30">
         <f>-G45*G48</f>
         <v>-331.99846637612239</v>
       </c>
-      <c r="H155" s="30">
+      <c r="H157" s="30">
         <f>-H45*H48</f>
         <v>-416.61064694969423</v>
       </c>
-      <c r="I155" s="30">
+      <c r="I157" s="30">
         <f>-I45*I48</f>
         <v>-457.43849035076425</v>
       </c>
-      <c r="J155" s="30">
+      <c r="J157" s="30">
         <f>-J45*J48</f>
         <v>-502.24894016808918</v>
       </c>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B156" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C156" s="30">
-        <v>200</v>
-      </c>
-      <c r="D156" s="30">
-        <v>170</v>
-      </c>
-      <c r="E156" s="30">
-        <v>-52</v>
-      </c>
-      <c r="F156" s="30">
-        <v>0</v>
-      </c>
-      <c r="G156" s="30">
-        <v>0</v>
-      </c>
-      <c r="H156" s="30">
-        <v>0</v>
-      </c>
-      <c r="I156" s="30">
-        <v>0</v>
-      </c>
-      <c r="J156" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B157" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C157" s="30">
-        <v>-17772</v>
-      </c>
-      <c r="D157" s="30">
-        <v>-20633</v>
-      </c>
-      <c r="E157" s="30">
-        <v>-18963</v>
-      </c>
-      <c r="F157" s="30">
-        <f>SUM(F150:F156)</f>
-        <v>-23683.681111249414</v>
-      </c>
-      <c r="G157" s="30">
-        <f t="shared" ref="G157:J157" si="21">SUM(G150:G156)</f>
-        <v>-26960.482727766135</v>
-      </c>
-      <c r="H157" s="30">
-        <f t="shared" si="21"/>
-        <v>-29676.216135549461</v>
-      </c>
-      <c r="I157" s="30">
-        <f t="shared" si="21"/>
-        <v>-32374.062962246117</v>
-      </c>
-      <c r="J157" s="30">
-        <f t="shared" si="21"/>
-        <v>-36109.322728110237</v>
-      </c>
-    </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="9" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C158" s="30">
-        <v>636</v>
+        <v>200</v>
       </c>
       <c r="D158" s="30">
-        <v>382</v>
+        <v>170</v>
       </c>
       <c r="E158" s="30">
-        <v>420</v>
+        <v>-52</v>
       </c>
       <c r="F158" s="30">
         <v>0</v>
@@ -5545,266 +5624,303 @@
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C159" s="30">
+        <v>-17772</v>
+      </c>
+      <c r="D159" s="30">
+        <v>-20633</v>
+      </c>
+      <c r="E159" s="30">
+        <v>-18963</v>
+      </c>
+      <c r="F159" s="30">
+        <f>SUM(F152:F158)</f>
+        <v>-23683.681111249414</v>
+      </c>
+      <c r="G159" s="30">
+        <f t="shared" ref="G159:J159" si="25">SUM(G152:G158)</f>
+        <v>-26960.482727766135</v>
+      </c>
+      <c r="H159" s="30">
+        <f t="shared" si="25"/>
+        <v>-29676.216135549461</v>
+      </c>
+      <c r="I159" s="30">
+        <f t="shared" si="25"/>
+        <v>-32374.062962246117</v>
+      </c>
+      <c r="J159" s="30">
+        <f t="shared" si="25"/>
+        <v>-36109.322728110237</v>
+      </c>
+    </row>
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B160" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C160" s="30">
+        <v>636</v>
+      </c>
+      <c r="D160" s="30">
+        <v>382</v>
+      </c>
+      <c r="E160" s="30">
+        <v>420</v>
+      </c>
+      <c r="F160" s="30">
+        <v>0</v>
+      </c>
+      <c r="G160" s="30">
+        <v>0</v>
+      </c>
+      <c r="H160" s="30">
+        <v>0</v>
+      </c>
+      <c r="I160" s="30">
+        <v>0</v>
+      </c>
+      <c r="J160" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B161" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C159" s="30">
+      <c r="C161" s="30">
         <v>1613</v>
       </c>
-      <c r="D159" s="30">
+      <c r="D161" s="30">
         <v>-2227</v>
       </c>
-      <c r="E159" s="30">
+      <c r="E161" s="30">
         <v>5224</v>
       </c>
-      <c r="F159" s="30">
-        <f>F139+F148+F157+F158</f>
+      <c r="F161" s="30">
+        <f>F141+F150+F159+F160</f>
         <v>16856.128757407005</v>
       </c>
-      <c r="G159" s="30">
-        <f t="shared" ref="G159:J159" si="22">G139+G148+G157+G158</f>
+      <c r="G161" s="30">
+        <f t="shared" ref="G161:J161" si="26">G141+G150+G159+G160</f>
         <v>17918.073311422912</v>
       </c>
-      <c r="H159" s="30">
-        <f t="shared" si="22"/>
+      <c r="H161" s="30">
+        <f t="shared" si="26"/>
         <v>19624.199034686731</v>
       </c>
-      <c r="I159" s="30">
-        <f t="shared" si="22"/>
+      <c r="I161" s="30">
+        <f t="shared" si="26"/>
         <v>21931.526161751532</v>
       </c>
-      <c r="J159" s="30">
-        <f t="shared" si="22"/>
+      <c r="J161" s="30">
+        <f t="shared" si="26"/>
         <v>23543.180362592495</v>
       </c>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B160" s="17" t="s">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B162" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C160" s="30">
+      <c r="C162" s="30">
         <v>20377</v>
       </c>
-      <c r="D160" s="30">
+      <c r="D162" s="30">
         <v>21990</v>
       </c>
-      <c r="E160" s="30">
+      <c r="E162" s="30">
         <v>19763</v>
       </c>
-      <c r="F160" s="30">
-        <f>E161</f>
+      <c r="F162" s="30">
+        <f>E163</f>
         <v>24987</v>
       </c>
-      <c r="G160" s="30">
-        <f>F161</f>
+      <c r="G162" s="30">
+        <f>F163</f>
         <v>41843.128757407001</v>
       </c>
-      <c r="H160" s="30">
-        <f t="shared" ref="H160:J160" si="23">G161</f>
+      <c r="H162" s="30">
+        <f t="shared" ref="H162:J162" si="27">G163</f>
         <v>59761.202068829909</v>
       </c>
-      <c r="I160" s="30">
-        <f t="shared" si="23"/>
+      <c r="I162" s="30">
+        <f t="shared" si="27"/>
         <v>79385.401103516633</v>
       </c>
-      <c r="J160" s="30">
-        <f t="shared" si="23"/>
+      <c r="J162" s="30">
+        <f t="shared" si="27"/>
         <v>101316.92726526817</v>
       </c>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B161" s="19" t="s">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B163" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C161" s="38">
+      <c r="C163" s="38">
         <v>21990</v>
       </c>
-      <c r="D161" s="38">
+      <c r="D163" s="38">
         <v>19763</v>
       </c>
-      <c r="E161" s="38">
+      <c r="E163" s="38">
         <v>24987</v>
       </c>
-      <c r="F161" s="38">
-        <f>F160+F159</f>
+      <c r="F163" s="38">
+        <f>F162+F161</f>
         <v>41843.128757407001</v>
       </c>
-      <c r="G161" s="38">
-        <f t="shared" ref="G161:J161" si="24">G160+G159</f>
+      <c r="G163" s="38">
+        <f t="shared" ref="G163:J163" si="28">G162+G161</f>
         <v>59761.202068829909</v>
       </c>
-      <c r="H161" s="38">
-        <f t="shared" si="24"/>
+      <c r="H163" s="38">
+        <f t="shared" si="28"/>
         <v>79385.401103516633</v>
       </c>
-      <c r="I161" s="38">
-        <f t="shared" si="24"/>
+      <c r="I163" s="38">
+        <f t="shared" si="28"/>
         <v>101316.92726526817</v>
       </c>
-      <c r="J161" s="38">
-        <f t="shared" si="24"/>
+      <c r="J163" s="38">
+        <f t="shared" si="28"/>
         <v>124860.10762786066</v>
       </c>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B162" s="10" t="s">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B164" s="10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B163" s="9" t="s">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B165" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C163" s="37">
+      <c r="C165" s="37">
         <v>3433</v>
       </c>
-      <c r="D163" s="37">
+      <c r="D165" s="37">
         <v>5775</v>
       </c>
-      <c r="E163" s="37">
+      <c r="E165" s="37">
         <v>4541</v>
       </c>
-      <c r="F163" s="37">
+      <c r="F165" s="37">
         <f>F64</f>
         <v>5497.0325000000012</v>
       </c>
-      <c r="G163" s="37">
-        <f t="shared" ref="G163:J163" si="25">G64</f>
+      <c r="G165" s="37">
+        <f t="shared" ref="G165:J165" si="29">G64</f>
         <v>6042.9902539224931</v>
       </c>
-      <c r="H163" s="37">
-        <f t="shared" si="25"/>
+      <c r="H165" s="37">
+        <f t="shared" si="29"/>
         <v>6638.7473784719532</v>
       </c>
-      <c r="I163" s="37">
-        <f t="shared" si="25"/>
+      <c r="I165" s="37">
+        <f t="shared" si="29"/>
         <v>7341.7715960398582</v>
       </c>
-      <c r="J163" s="37">
-        <f t="shared" si="25"/>
+      <c r="J165" s="37">
+        <f t="shared" si="29"/>
         <v>8071.0032838196794</v>
       </c>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B164" s="9" t="s">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B166" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C164" s="37">
+      <c r="C166" s="37">
         <v>617</v>
       </c>
-      <c r="D164" s="37">
+      <c r="D166" s="37">
         <v>583</v>
       </c>
-      <c r="E164" s="37">
+      <c r="E166" s="37">
         <v>587</v>
       </c>
-      <c r="F164" s="37">
+      <c r="F166" s="37">
         <f>ABS(F60)</f>
         <v>589</v>
       </c>
-      <c r="G164" s="37">
-        <f t="shared" ref="G164:J164" si="26">ABS(G60)</f>
+      <c r="G166" s="37">
+        <f t="shared" ref="G166:J166" si="30">ABS(G60)</f>
         <v>589</v>
       </c>
-      <c r="H164" s="37">
-        <f t="shared" si="26"/>
+      <c r="H166" s="37">
+        <f t="shared" si="30"/>
         <v>589</v>
       </c>
-      <c r="I164" s="37">
-        <f t="shared" si="26"/>
+      <c r="I166" s="37">
+        <f t="shared" si="30"/>
         <v>589</v>
       </c>
-      <c r="J164" s="37">
-        <f t="shared" si="26"/>
+      <c r="J166" s="37">
+        <f t="shared" si="30"/>
         <v>589</v>
       </c>
     </row>
-    <row r="165" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="20" t="s">
+    <row r="167" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C165" s="36">
+      <c r="C167" s="36">
         <v>96</v>
       </c>
-      <c r="D165" s="36">
+      <c r="D167" s="36">
         <v>52</v>
       </c>
-      <c r="E165" s="36">
+      <c r="E167" s="36">
         <v>59</v>
       </c>
-      <c r="F165" s="36">
-        <v>0</v>
-      </c>
-      <c r="G165" s="36">
-        <v>0</v>
-      </c>
-      <c r="H165" s="36">
-        <v>0</v>
-      </c>
-      <c r="I165" s="36">
-        <v>0</v>
-      </c>
-      <c r="J165" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B167" s="1" t="s">
+      <c r="F167" s="36">
+        <v>0</v>
+      </c>
+      <c r="G167" s="36">
+        <v>0</v>
+      </c>
+      <c r="H167" s="36">
+        <v>0</v>
+      </c>
+      <c r="I167" s="36">
+        <v>0</v>
+      </c>
+      <c r="J167" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B169" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C169" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="D169" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E167" s="3" t="s">
+      <c r="E169" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F167" s="2" t="s">
+      <c r="F169" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="G169" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H167" s="2" t="s">
+      <c r="H169" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I167" s="2" t="s">
+      <c r="I169" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J167" s="2" t="s">
+      <c r="J169" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B168" s="42" t="s">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B170" s="42" t="s">
         <v>141</v>
-      </c>
-      <c r="C168" s="40"/>
-      <c r="D168" s="40"/>
-      <c r="E168" s="40"/>
-      <c r="F168" s="41"/>
-      <c r="G168" s="41"/>
-      <c r="H168" s="41"/>
-      <c r="I168" s="41"/>
-      <c r="J168" s="41"/>
-    </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B169" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="C169" s="40"/>
-      <c r="D169" s="40"/>
-      <c r="E169" s="40"/>
-      <c r="F169" s="41"/>
-      <c r="G169" s="41"/>
-      <c r="H169" s="41"/>
-      <c r="I169" s="41"/>
-      <c r="J169" s="41"/>
-    </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B170" s="43" t="s">
-        <v>143</v>
       </c>
       <c r="C170" s="40"/>
       <c r="D170" s="40"/>
@@ -5817,7 +5933,7 @@
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="43" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C171" s="40"/>
       <c r="D171" s="40"/>
@@ -5830,7 +5946,7 @@
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="43" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C172" s="40"/>
       <c r="D172" s="40"/>
@@ -5840,6 +5956,32 @@
       <c r="H172" s="41"/>
       <c r="I172" s="41"/>
       <c r="J172" s="41"/>
+    </row>
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B173" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C173" s="40"/>
+      <c r="D173" s="40"/>
+      <c r="E173" s="40"/>
+      <c r="F173" s="41"/>
+      <c r="G173" s="41"/>
+      <c r="H173" s="41"/>
+      <c r="I173" s="41"/>
+      <c r="J173" s="41"/>
+    </row>
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B174" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="C174" s="40"/>
+      <c r="D174" s="40"/>
+      <c r="E174" s="40"/>
+      <c r="F174" s="41"/>
+      <c r="G174" s="41"/>
+      <c r="H174" s="41"/>
+      <c r="I174" s="41"/>
+      <c r="J174" s="41"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
